--- a/tests/integration_workspace/dashboard_full_pipeline/output/MASTER_DATASET.xlsx
+++ b/tests/integration_workspace/dashboard_full_pipeline/output/MASTER_DATASET.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER_MATCH" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MASTER_DATASET" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,25 +424,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>CATEGORY</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>BRAND</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Variant</t>
+          <t>VARIANT</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>VOLUME</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>AROMA</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>MASTER_NAME</t>
         </is>
@@ -476,6 +496,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>APPLE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Шампунь SVO APPLE 1 л</t>
         </is>
       </c>
@@ -507,6 +535,14 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>LIME</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Шампунь SVO LIME 1 л</t>
         </is>
